--- a/www/download/IND.capital_stock.s.us.WIOD16.xlsx
+++ b/www/download/IND.capital_stock.s.us.WIOD16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>1253196.36408681</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>1172460.03416428</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1323766.35526373</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.727</t>
+          <t>1727132.11316263</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2.123</t>
+          <t>2122536.36206987</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2.399</t>
+          <t>2399001.02984087</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2.573</t>
+          <t>2572834.15442542</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>3.092</t>
+          <t>3092050.26927516</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3.326</t>
+          <t>3326029.84298293</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3.219</t>
+          <t>3218631.36744093</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>3.927</t>
+          <t>3927046.85311161</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>4.642</t>
+          <t>4641830.82241605</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>4.937</t>
+          <t>4937348.89207421</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>4.903</t>
+          <t>4902934.79359827</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>4.814</t>
+          <t>4813985.77263268</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>713755.771</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>714189.59256</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>773895.20976</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>959604.53904</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1099885.73604</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>1148216.46654</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1.216</t>
+          <t>1215615.418</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>1407231.45575</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.592</t>
+          <t>1591984.94812</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>1561523.65204</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.537</t>
+          <t>1537288.21593</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>1674537.72</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.601</t>
+          <t>1600804.52576</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1.709</t>
+          <t>1709213.83377</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>1762056.63925</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>672915.7481964</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.675</t>
+          <t>674669.00356</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>725912.5353456</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.903</t>
+          <t>902703.7073488</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.037</t>
+          <t>1036744.99887</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>1086579.02496</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.166</t>
+          <t>1166031.9008156</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1340280.3365795</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1533998.36396</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1457587.6207948</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1428485.63067</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1558587.324384</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1484992.3968</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1559776.95144</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1581773.66498213</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45856.7321918828</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48104.1667126075</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52850.9585545782</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64768.4327098009</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77277.3992290491</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90124.2521992096</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104004.763114836</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>130417.183581926</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>166844.501980044</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>173949.005470509</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>168766.469796782</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>193177.844510688</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>184979.705188932</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>194261.990886119</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>198266.253205199</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.209</t>
+          <t>2208829.95626249</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.918</t>
+          <t>1917765.26549577</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.852</t>
+          <t>1851935.52144764</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.897</t>
+          <t>1896832.45194088</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.189</t>
+          <t>2188885.36879494</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.743</t>
+          <t>2742637.2953084</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.085</t>
+          <t>3085499.84878598</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.733</t>
+          <t>3733034.77112992</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.484</t>
+          <t>4483591.68792562</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.658</t>
+          <t>4657916.79617169</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>5.957</t>
+          <t>5956607.76078443</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>6.997</t>
+          <t>6997070.08039855</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>6.902</t>
+          <t>6902478.83828462</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>6.936</t>
+          <t>6935785.39069556</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>7.455</t>
+          <t>7454852.05712726</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1243561.0424159</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1250506.3519049</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>1297375.86688009</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1523421.87676619</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>1762105.31904669</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2.033</t>
+          <t>2032807.62136916</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2.381</t>
+          <t>2380680.4417531</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2.765</t>
+          <t>2765310.34839756</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3050357.62235043</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.893</t>
+          <t>2893179.40399061</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>3.353</t>
+          <t>3352555.4521423</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>3.687</t>
+          <t>3687026.91955812</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3.887</t>
+          <t>3886529.85079441</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>3.964</t>
+          <t>3963632.55681866</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3.906</t>
+          <t>3906433.68259294</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.994</t>
+          <t>2993742.86980939</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.358</t>
+          <t>3358259.88283325</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.788</t>
+          <t>3787643.71776461</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4.422</t>
+          <t>4422157.31166924</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5.326</t>
+          <t>5325574.17921317</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6.376</t>
+          <t>6376393.7018432</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7.636</t>
+          <t>7635752.34695555</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>9.346</t>
+          <t>9346399.27334974</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>12.592</t>
+          <t>12592008.0238074</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>14.292</t>
+          <t>14292423.3597335</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>17.111</t>
+          <t>17111423.3990992</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>21.877</t>
+          <t>21876816.7470749</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>25580489.5361577</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>29.478</t>
+          <t>29478137.609998</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>32.899</t>
+          <t>32898860.3425465</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29661.0580100393</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30051.6760931552</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33346.1213783102</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41113.9197689739</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48864.1877031138</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52795.347969346</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57185.9760614962</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66427.8852070619</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78948.1446462889</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75840.8956615264</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74824.8657112741</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78445.0829796137</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71941.2256023233</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73285.144235548</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73360.0148954629</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>303872.26426</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>322838.6372376</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>385912.4163873</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>460142.0284204</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>530229.337704</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.591</t>
+          <t>591082.8709555</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>657880.4847976</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>797369.358772</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1.014</t>
+          <t>1013990.6817318</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>912380.1138829</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.907</t>
+          <t>907078.0873175</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>990068.4144862</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>893574.9319144</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>896508.4538655</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>863711.6749155</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.265</t>
+          <t>6264655.0376</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.172</t>
+          <t>6172258.4648</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6.567</t>
+          <t>6566673.8112</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7.909</t>
+          <t>7908772.3568</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8.851</t>
+          <t>8850763.9626</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>8.982</t>
+          <t>8982103.416</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9.319</t>
+          <t>9319358.266</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>10.777</t>
+          <t>10777340.641</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>12.019</t>
+          <t>12018711.3276</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>11.559</t>
+          <t>11559152.5412</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>11.175</t>
+          <t>11174559.9489</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>12.145</t>
+          <t>12144977.28</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>11.577</t>
+          <t>11576806.032</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>12.309</t>
+          <t>12309141.5754</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>12.646</t>
+          <t>12645545.6859586</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>514524.956634</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>526100.86235</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>570323.157355</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>707835.496493</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>800956.303329</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>836391.500357</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.907</t>
+          <t>906993.822735</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>1047668.4037</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>1159038.56538</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.035</t>
+          <t>1035315.222315</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>1023709.42443</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>1104155.06244245</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1044553.070396</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>1091189.13551</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>1.115</t>
+          <t>1115378.66927521</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1587831.6499944</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.679</t>
+          <t>1679430.7464096</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1940205.7568784</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.539</t>
+          <t>2539117.6009472</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>3.095</t>
+          <t>3095010.8771442</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3.434</t>
+          <t>3434280.4407054</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3.841</t>
+          <t>3840991.7867872</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>4.529</t>
+          <t>4528697.723213</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>5.144</t>
+          <t>5144392.5049796</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>4.829</t>
+          <t>4828920.6394924</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>4.621</t>
+          <t>4620921.5451645</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>4.822</t>
+          <t>4821965.178048</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>4.329</t>
+          <t>4328866.1586016</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4309961.4287715</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>4.296</t>
+          <t>4296159.82321717</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14854.0688350661</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17642.0975731334</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19465.8564937375</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26009.8969187024</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32944.341824537</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37026.1701857779</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44789.0932095577</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59360.1940186161</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67380.5336649981</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62899.3125906776</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60123.9353766553</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67160.8273697215</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66676.6684373134</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76581.2660947353</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79706.5825745033</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>371077.5428</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>381527.3912</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>405728.592</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>494505.2112</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>566792.9862</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>602515.1418</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>641462.1836</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>757575.3965</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>873103.65</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>823968.3364</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>770120.3412</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>844318.992</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>824420.1856</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>869707.6131</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>882057.575</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.723</t>
+          <t>3722862.5812</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.784</t>
+          <t>3783614.4537912</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4.175</t>
+          <t>4175276.9414544</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>5.261</t>
+          <t>5260731.5712</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6.115</t>
+          <t>6115391.7882561</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>6.495</t>
+          <t>6495303.0272559</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>6.984</t>
+          <t>6984335.2662888</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>8.152</t>
+          <t>8151868.3076295</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>9.124</t>
+          <t>9124454.9088</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>8.792</t>
+          <t>8791590.3825948</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>8.673</t>
+          <t>8673233.1633486</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>9.489</t>
+          <t>9489138.721392</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>8979715.172824</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>9.429</t>
+          <t>9429114.2208876</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>9.525</t>
+          <t>9524999.86811111</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3339585.52863</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.366</t>
+          <t>3366478.16412</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3729779.88558</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4.289</t>
+          <t>4289149.10328</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>5.104</t>
+          <t>5104312.5318</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>5.515</t>
+          <t>5514643.3032</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>5.884</t>
+          <t>5884164.35313</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>6.825</t>
+          <t>6824812.03056</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>6.773</t>
+          <t>6773486.56532</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>5.724</t>
+          <t>5724219.55072</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>5.689</t>
+          <t>5689083.36321</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>6.119</t>
+          <t>6118673.7096</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>6.237</t>
+          <t>6237408.53624</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>6.399</t>
+          <t>6399489.56652</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>6.939</t>
+          <t>6939428.91342</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>422177.192035329</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>451785.252831652</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>483856.45015616</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>516015.775403531</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>546921.425570403</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>560549.550997327</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>613615.906611696</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>650282.901088862</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>689927.048663309</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>698311.242184979</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>689525.663213687</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>667295.16834761</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>651113.190052215</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>647845.08654333</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>630182.428973513</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>221912.45957304</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>238870.439199676</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>280745.257041739</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>342718.129409854</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>402410.731562834</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>431350.285276898</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>445519.00923802</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>547909.126799881</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>631333.466278238</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>558249.666539423</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>552111.452277222</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.587</t>
+          <t>587205.424204613</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>534262.242358152</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>550723.040794777</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>545284.418647407</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>550799.648698728</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.503</t>
+          <t>502771.859258796</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>582483.903597909</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>701723.91456149</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>786384.108109911</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>853145.516452215</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1110204.13755865</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.284</t>
+          <t>1284168.71246861</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1504807.37619439</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.816</t>
+          <t>1815886.33513375</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2.369</t>
+          <t>2369022.40123853</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2.744</t>
+          <t>2743962.45553503</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2.863</t>
+          <t>2862778.3551911</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2.821</t>
+          <t>2821318.31958435</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2.824</t>
+          <t>2823587.58599551</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.259</t>
+          <t>1259248.34376209</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1314868.07418997</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.377</t>
+          <t>1377426.97855563</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>1610678.88373165</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.927</t>
+          <t>1926648.53401267</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2209560.42545759</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2.482</t>
+          <t>2482476.39621009</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>3.171</t>
+          <t>3170969.84644305</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3.533</t>
+          <t>3532815.94243658</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>3.603</t>
+          <t>3603373.34265588</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>4.413</t>
+          <t>4412868.90443772</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>5.075</t>
+          <t>5074613.97489521</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>5.347</t>
+          <t>5346701.1591533</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5700423.07142781</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>6.166</t>
+          <t>6166054.3035903</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>210488.082094703</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>235338.784501443</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>279697.093862628</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>377725.448382955</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>474648.271376918</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>539236.923988292</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>610118.312572804</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>685810.913922469</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>680194.349283315</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>579066.535980496</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.532</t>
+          <t>532316.500900772</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>564394.791114537</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>542576.250201426</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>581300.426743562</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>636832.894770653</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.223</t>
+          <t>3223486.7455164</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.259</t>
+          <t>3259007.6150888</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3.627</t>
+          <t>3627195.4560144</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4.521</t>
+          <t>4520792.0486736</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5249822.9831117</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>5.552</t>
+          <t>5551876.3675518</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>5.862</t>
+          <t>5861830.2537268</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>6.748</t>
+          <t>6748424.2231475</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>7.619</t>
+          <t>7619395.1172768</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>7.395</t>
+          <t>7395407.8582296</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>7.251</t>
+          <t>7250760.9131814</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>7.942</t>
+          <t>7941866.690784</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7430259.7360288</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>7.675</t>
+          <t>7675377.5598195</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>7.666</t>
+          <t>7665812.06199564</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>12.929</t>
+          <t>12929335.5367143</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11.916</t>
+          <t>11916248.1822585</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11.931</t>
+          <t>11930682.2949141</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>13.133</t>
+          <t>13133073.3797242</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>14.175</t>
+          <t>14175074.1519047</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>14.014</t>
+          <t>14014397.2369244</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>13.222</t>
+          <t>13222088.9201837</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>12.973</t>
+          <t>12972963.6033805</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>14.465</t>
+          <t>14464963.8271289</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>16.38</t>
+          <t>16379891.3059061</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>17.531</t>
+          <t>17530536.5673627</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>19.107</t>
+          <t>19107114.3572554</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>19.114</t>
+          <t>19113785.2474752</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>15.486</t>
+          <t>15485864.1604196</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>13.976</t>
+          <t>13975539.7359382</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.761</t>
+          <t>1760763.02574163</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.696</t>
+          <t>1696279.87140151</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.924</t>
+          <t>1923951.98913888</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.254</t>
+          <t>2254483.10084743</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.625</t>
+          <t>2625495.85987795</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3.148</t>
+          <t>3148067.45678187</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3.623</t>
+          <t>3623140.12525721</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4050112.62600163</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4010334.68967057</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3.689</t>
+          <t>3688646.56784979</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>4.192</t>
+          <t>4192191.68889788</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>4.906</t>
+          <t>4905598.55377011</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>5.084</t>
+          <t>5084424.89302055</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>5.507</t>
+          <t>5507076.66993928</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>6.027</t>
+          <t>6027281.27876362</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41361.3510292618</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41880.8203712866</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46802.5548466953</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59302.2589503403</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71160.8708480923</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79539.3281152391</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92566.0323977185</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118291.893736853</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>133711.292460252</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120013.070819408</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113843.017324706</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>125610.666707677</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>121690.25964673</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131534.430977248</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136594.727486177</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44399.6581512182</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46815.6370370695</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52233.315591562</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>65337.5964640435</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76299.024647537</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80867.7530151146</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86177.7192967943</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100766.449641372</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116367.833799383</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>115267.432635396</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114250.808400574</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127542.610285798</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>125418.102444949</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>136161.243830329</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143361.754943028</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22538.3633860872</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23138.6393275626</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23153.8774156127</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26947.8853815616</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32516.2005095119</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37770.2201613247</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47508.6885524661</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72491.309786885</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91533.8330476895</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>73959.9939502697</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73304.3094847676</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82569.9458065045</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>84429.6158581416</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90543.0905228617</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93269.5045477395</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>1722624.36042529</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.879</t>
+          <t>1879112.44835813</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.942</t>
+          <t>1942336.83246301</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.906</t>
+          <t>1905592.94848892</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2010008.91075313</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2219810.17455009</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2.433</t>
+          <t>2432658.93487484</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2.591</t>
+          <t>2591383.06842127</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2.827</t>
+          <t>2826610.31516828</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.505</t>
+          <t>2504913.57377432</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2.806</t>
+          <t>2805901.24956789</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>3.079</t>
+          <t>3079158.84245708</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>3.118</t>
+          <t>3117956.34962214</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3250163.91711135</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>3.293</t>
+          <t>3292534.20970022</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10579.1306865473</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11021.5764852424</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12039.2294788405</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14331.8630927035</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16233.6780725241</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16734.0385936516</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18769.599064396</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22307.3358096678</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26567.3245566894</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26538.6946478904</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26020.5938311373</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28456.5293535819</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27623.132965109</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29183.7326324026</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30325.7216933288</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1194810.4287164</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.242</t>
+          <t>1242319.0024956</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>1394372.304</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>1748095.50832</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.986</t>
+          <t>1985838.3367039</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2.052</t>
+          <t>2052235.5097959</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2.169</t>
+          <t>2169264.20984</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2.468</t>
+          <t>2468266.2500795</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2.785</t>
+          <t>2784890.6709292</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2.743</t>
+          <t>2742650.1937252</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2.668</t>
+          <t>2668233.0797271</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2.806</t>
+          <t>2806085.196384</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2.594</t>
+          <t>2594452.5288</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2.687</t>
+          <t>2687139.4189281</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2.673</t>
+          <t>2672996.4671715</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>307313.953804102</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>340997.335679587</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>353479.913302993</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>385616.739707989</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>423034.383629644</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>489936.592558011</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>523846.516189478</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>658801.363701881</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>812273.123565822</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>650963.572485059</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>712105.196720569</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>775351.707819101</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>729179.511186234</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>780564.876396757</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>816429.916862391</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>271986.310390906</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>281336.713412227</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>320423.494078458</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>399704.797574366</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>467782.789090641</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>492256.72487889</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>585505.987160937</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>678425.465774138</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>799044.275191761</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>771899.208122596</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>754527.396850811</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>813659.141830659</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>742730.741974841</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>765300.457405339</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>786213.11316623</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>128284.008829398</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139477.559335078</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153537.51117354</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>189262.08899412</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>226913.435796682</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>291158.774454879</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>341341.290727237</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>462092.457192344</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>551072.318318459</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>484330.370315251</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>510452.10001564</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>586432.05711185</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>560965.936714791</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>607485.269119921</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>616337.951745181</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>900289.312167438</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>1011315.26768526</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>1080682.59854099</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1243785.8260353</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1566851.4496426</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.849</t>
+          <t>1849121.18360728</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2.252</t>
+          <t>2252121.7569958</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.958</t>
+          <t>2957876.22634916</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>3.778</t>
+          <t>3777705.66350131</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3089859.86436662</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>3675424.27180718</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>4.322</t>
+          <t>4321715.08929451</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4640419.48795297</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>4.934</t>
+          <t>4934341.71216641</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>4.649</t>
+          <t>4648715.19728378</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>124815.596975232</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>130105.422886244</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>149048.71543557</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>190665.861539377</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>227438.027389066</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>253107.862868188</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>277682.411273661</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>345677.632379492</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>435614.218315439</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>436511.621329372</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>418214.007566577</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>447692.025833042</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>417052.932650754</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>442940.768063548</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>456045.182311835</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70077.6380364196</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69641.7752295007</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74872.7648766688</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93050.1990637697</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110192.883584786</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118564.843403705</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126865.445390535</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>150212.437460841</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>173680.254313919</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>167577.66961286</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>163108.410917758</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175885.573885247</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>164311.630729851</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171418.39878552</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>172050.330956768</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>662040.983818531</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>636824.493535603</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>713731.644491386</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>891477.023350319</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>1028065.49717087</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1057625.54022889</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>1133268.58628414</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1325522.22809635</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1498462.19943231</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1.352</t>
+          <t>1351703.74012876</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1.481</t>
+          <t>1481083.079584</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>1704120.48106881</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1.686</t>
+          <t>1685527.3598538</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>1.804</t>
+          <t>1803772.91324202</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1790168.69205463</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>614374.722303938</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>516854.10752241</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>521436.964823224</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>630339.094475198</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>790552.603058632</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.903</t>
+          <t>902575.944559943</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>1028360.06758582</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1200274.59613604</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1532112.16039502</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.372</t>
+          <t>1371525.38480416</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1466155.97759113</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1618664.68648815</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.645</t>
+          <t>1644655.7948755</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1.736</t>
+          <t>1736114.02768674</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>1.761</t>
+          <t>1761056.4551636</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>677024.512003141</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>640830.069077162</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>653015.193307648</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>694141.77058884</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>817476.028520209</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>879770.747430619</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>947568.095251788</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>1.021</t>
+          <t>1021361.04184221</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1.184</t>
+          <t>1183648.78102227</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1.109</t>
+          <t>1109101.8251892</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1226245.50895792</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1.393</t>
+          <t>1392500.59039185</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1430472.33325257</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1448319.78776885</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>1.479</t>
+          <t>1479244.17096199</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>27.927</t>
+          <t>27926969.0053173</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>29.491</t>
+          <t>29490972.0495477</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>30.943</t>
+          <t>30942872.995062</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>32.646</t>
+          <t>32645919.0643944</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>35.988</t>
+          <t>35987652.0362497</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>39629875.0508333</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>42.855</t>
+          <t>42855464.9967933</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>44.747</t>
+          <t>44746686.9858048</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>46.192</t>
+          <t>46192289.9759759</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>45.273</t>
+          <t>45273493.9909204</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>46.192</t>
+          <t>46191595.0277175</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>47.651</t>
+          <t>47650756.9159532</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>49.154</t>
+          <t>49153970.1324136</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>51.528</t>
+          <t>51527646.9536609</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>53.547</t>
+          <t>53547021.0467933</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8.865</t>
+          <t>8865433.2634179</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8.933</t>
+          <t>8932611.01263824</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8.876</t>
+          <t>8875898.6632211</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>10.105</t>
+          <t>10104545.3223379</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>11.913</t>
+          <t>11913431.585164</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>14.159</t>
+          <t>14159359.795553</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>16.271</t>
+          <t>16271374.6995712</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>18.998</t>
+          <t>18998393.1230342</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>22.614</t>
+          <t>22613884.4298864</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>22.319</t>
+          <t>22318804.4685833</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>25.893</t>
+          <t>25892984.1570922</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>30.277</t>
+          <t>30276753.1382179</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>33.112</t>
+          <t>33112399.3111959</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>33.912</t>
+          <t>33911748.8997174</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>34.523</t>
+          <t>34523031.7458068</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>90.724</t>
+          <t>90723840.6694089</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>91.771</t>
+          <t>91771183.0822633</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.862</t>
+          <t>96862432.2529047</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>109.641</t>
+          <t>109641205.323408</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>124.556</t>
+          <t>124556428.815013</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>136.327</t>
+          <t>136327343.725308</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>147.764</t>
+          <t>147763940.548064</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>165.294</t>
+          <t>165294229.808337</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>184.522</t>
+          <t>184522328.27655</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>182.203</t>
+          <t>182203128.545811</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>195.269</t>
+          <t>195269241.917272</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>217.383</t>
+          <t>217382827.584967</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>223.974</t>
+          <t>223974131.252149</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>231.217</t>
+          <t>231217016.365275</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>238.116</t>
+          <t>238115877.478904</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67128.8973838885</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68348.7251160496</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77624.0784561411</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98466.1562108934</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>119748.231412554</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129901.630369209</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>143914.59109527</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171975.873266776</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>200442.140863078</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>188542.672866955</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>174065.868749431</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>181737.676074269</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162149.66181013</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162405.748038515</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158969.7574768</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>776679.759012353</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>786154.772669633</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>825880.569415599</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>973594.036236475</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1060391.57377992</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1.089</t>
+          <t>1088755.89216615</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>1119107.53864174</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>1237333.47775683</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1460683.642851</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1.506</t>
+          <t>1506433.79002768</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1595339.2815254</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1.923</t>
+          <t>1923231.17137278</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1.878</t>
+          <t>1877856.13407336</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1952322.87670861</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2.013</t>
+          <t>2013272.65260047</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>436115.207490924</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>450358.784317831</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>522856.905898737</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>599820.983801101</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>679159.523636757</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>768291.74424481</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>844000.213257616</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1029605.06014961</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1179640.13277467</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1110706.35252739</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1.201</t>
+          <t>1201226.02613738</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1384901.39606438</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1413383.49397177</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>1.479</t>
+          <t>1479257.9756484</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1471086.95179907</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>capital_stock.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
